--- a/data_extactor/batch_10_fa/trimmed/batch_0037_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0037_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | نگارش | سخن گفتن | نظارت | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
+          <t>راهبردهای یادگیری | نگارش | سخن گفتن | نظارت | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | مدیریت و امور اداری | ریاضیات | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | روان‌شناسی</t>
+          <t>آموزش و پرورش | مدیریت و اداره | ریاضیات | رایانه و الکترونیک | خدمات مشتری و شخصی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران آموزشی دوره‌های پیش‌دبستانی تا متوسطه | استادان علوم تربیتی آموزش عالی | مشاوران تحصیلی، شغلی و تربیتی | آموزگاران دوره ابتدایی (به‌جز استثنایی) | دبیران دوره اول متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | راهبردهای یادگیری | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | راهبردهای یادگیری | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | روان‌شناسی | ریاضیات | آموزش و تدریس | ایمنی و امنیت عمومی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | ریاضیات | آموزش و پرورش | ایمنی و امنیت عمومی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | وضوح گفتار | حساسیت به مسئله | بیان کتبی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | وضوح گفتار | حساسیت به مسئله | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران آموزشی دوره‌های پیش‌دبستانی تا متوسطه | آموزگاران دوره ابتدایی (به‌جز استثنایی) | مربیان پیش‌دبستانی (به‌جز استثنایی) | دبیران دوره اول متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | معلمان استثنایی دوره ابتدایی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | کمک‌معلمان آموزش استثنایی</t>
+          <t>مدیران آموزشی مقاطع ابتدایی و متوسطه | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | کمک‌معلمان آموزش استثنایی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | راهبردهای یادگیری | نظارت | تفکر انتقادی | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | راهبردهای یادگیری | نظارت | تفکر انتقادی | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | دید نزدیک | درک کتبی | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | بینایی نزدیک | درک کتبی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>آموزگاران دوره ابتدایی (به‌جز استثنایی) | مربیان پیش‌دبستانی (به‌جز استثنایی) | معلمان استثنایی دوره ابتدایی | معلمان استثنایی دوره پیش‌دبستانی | معلمان استثنایی دوره اول متوسطه | معلمان استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز استثنایی)</t>
+          <t>معلمان دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | راهبردهای یادگیری | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | راهبردهای یادگیری | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | رایانه و الکترونیک | ریاضیات</t>
+          <t>زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>استادان و مدرسان علوم زیستی آموزش عالی | استادان علوم تربیتی آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | استادان علوم ریاضی آموزش عالی | استادان روان‌شناسی آموزش عالی | استادان جامعه‌شناسی آموزش عالی | مدرسان و معلمان خصوصی</t>
+          <t>استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | استادان روان‌شناسی دانشگاه | استادان جامعه‌شناسی دانشگاه | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | رایانه و الکترونیک | ریاضیات</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک کتبی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز استثنایی) | کمک‌معلمان آموزش استثنایی | دستیاران آموزشی در آموزش عالی | مدرسان و معلمان خصوصی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | کاردان‌ها و تکنسین‌های کتابداری | مربیان و مراقبان کودک</t>
+          <t>کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | تکنسین‌های کتابداری | مربیان و مراقبان کودک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های کتابداری | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | آرشیوداران | کاردان‌ها و مرمت‌کاران موزه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | سایر کمک‌معلمان و دستیاران آموزشی | کارشناسان مدیریت اسناد و مدارک</t>
+          <t>تکنسین‌های کتابداری | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کارشناسان اسناد و آرشیو | تکنسین‌ها و مرمت‌گران موزه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | سایر کمک‌معلمان و دستیاران آموزشی | کارشناسان مدیریت اسناد و مدارک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>طراحی | زبان انگلیسی | رایانه و الکترونیک | هنرهای تجسمی | ارتباطات و رسانه | فروش و بازاریابی | خدمات مشتریان و خدمات فردی</t>
+          <t>طراحی | زبان انگلیسی | رایانه و الکترونیک | هنرهای زیبا | ارتباطات و رسانه | فروش و بازاریابی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ابتکار و اصالت | روانی و سیالی ایده‌ها | درک شفاهی | بیان شفاهی | دید نزدیک | تجسم فضایی | تشخیص رنگ‌ها</t>
+          <t>اصالت | روانی ایده‌ها | درک شفاهی | بیان شفاهی | بینایی نزدیک | تجسم | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تدوین‌گران فیلم و ویدئو | هنرمندان هنرهای تجسمی (نقاشان، مجسمه‌سازان و تصویرگران) | طراحان گرافیک | مدیران تامین و تولید برنامه‌های رسانه‌ای | تهیه‌کنندگان و کارگردانان | طراحان صحنه و دکور | پویانماها و طراحان جلوه‌های ویژه</t>
+          <t>تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | مدیران برنامه‌ریزی و پخش رسانه | تهیه‌کنندگان و کارگردانان | طراحان صحنه و نمایشگاه | پویانماها و طراحان جلوه‌های ویژه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>طراحی | هنرهای تجسمی | فروش و بازاریابی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | تولید و فراوری</t>
+          <t>طراحی | هنرهای زیبا | فروش و بازاریابی | زبان انگلیسی | خدمات مشتری و شخصی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ابتکار و اصالت | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دید نزدیک | روانی و سیالی ایده‌ها | تجسم فضایی</t>
+          <t>اصالت | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | بینایی نزدیک | روانی ایده‌ها | تجسم</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و درودگران کارگاهی | قلم‌زنان، کلیشه‌سازان و حکاکان | هنرمندان هنرهای تجسمی (نقاشان، مجسمه‌سازان و تصویرگران) | جواهرسازان و سازندگان مصنوعات فلزات و سنگ‌های قیمتی | رنگ‌کاران، پوشش‌کاران و تزیین‌کاران صنعتی و دستی | کوزه‌گران و سفالگران کارگاهی | دوزندگان و تعمیرکاران کفش و مصنوعات چرمی</t>
+          <t>کابینت‌سازان و نجاران کارگاهی | حکاکان و اسیدکاران | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | سفالگران خطوط تولید و کارگاهی | کارگران و تعمیرکاران کفش و چرم</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>یادگیری فعال | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>طراحی | رایانه و الکترونیک | تولید و فراوری | هنرهای تجسمی | آموزش و تدریس | ارتباطات و رسانه</t>
+          <t>طراحی | رایانه و الکترونیک | تولید و فرآوری | هنرهای زیبا | آموزش و پرورش | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ابتکار و اصالت | روانی و سیالی ایده‌ها | تجسم فضایی | ثبات دست و بازو | تشخیص رنگ‌ها | دید نزدیک | چابکی انگشتان</t>
+          <t>اصالت | روانی ایده‌ها | تجسم | ثبات دست و بازو | تشخیص رنگ بصری | بینایی نزدیک | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران هنری | هنرمندان صنایع دستی | قلم‌زنان، کلیشه‌سازان و حکاکان | طراحان گرافیک | طراحان دکوراسیون داخلی | عکاسان | پویانماها و طراحان جلوه‌های ویژه</t>
+          <t>مدیران هنری | هنرمندان صنایع دستی | حکاکان و اسیدکاران | طراحان گرافیک | طراحان داخلی | عکاسان | پویانماها و طراحان جلوه‌های ویژه</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | طراحی | ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | فنی و مهندسی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | طراحی | ارتباطات و رسانه | خدمات مشتری و شخصی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | تجسم فضایی | دید نزدیک | تشخیص رنگ‌ها | ابتکار و اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | تجسم | بینایی نزدیک | تشخیص رنگ بصری | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران هنری | فیلم‌برداران تلویزیون، ویدئو و سینما | برنامه‌نویسان رایانه | تدوین‌گران فیلم و ویدئو | طراحان گرافیک | طراحان بازی‌های رایانه‌ای | طراحان رابط کاربری و صفحات وب</t>
+          <t>مدیران هنری | تصویربرداران تلویزیون، ویدیو و سینما | برنامه‌نویسان کامپیوتر | تدوین‌گران فیلم و ویدیو | طراحان گرافیک | طراحان بازی‌های ویدیویی | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
